--- a/data/trans_dic/IP1020-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen transtornos crónicos de la piel</t>
+          <t>Menores que padecen transtornos crónicos de la piel (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,61</t>
+          <t>1,83; 7,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,99</t>
+          <t>0,41; 3,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,94</t>
+          <t>0,8; 8,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,57</t>
+          <t>0,56; 5,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,81</t>
+          <t>0,52; 5,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,97</t>
+          <t>0,3; 2,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,19</t>
+          <t>1,18; 4,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,43</t>
+          <t>0,73; 3,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,04</t>
+          <t>0,39; 4,19</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,53</t>
+          <t>0,25; 2,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,82</t>
+          <t>2,26; 6,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,32</t>
+          <t>0,52; 3,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,35</t>
+          <t>1,75; 7,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,2</t>
+          <t>0,24; 2,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,12</t>
+          <t>0,95; 3,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,49</t>
+          <t>0,64; 3,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 8,01</t>
+          <t>2,78; 8,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,78</t>
+          <t>0,37; 1,75</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,48</t>
+          <t>1,89; 4,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,64</t>
+          <t>0,81; 2,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,37</t>
+          <t>2,72; 6,34</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,44</t>
+          <t>0,3; 3,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,14</t>
+          <t>0,36; 3,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,1</t>
+          <t>1,67; 7,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,51</t>
+          <t>0,41; 4,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,24</t>
+          <t>0,37; 4,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,37</t>
+          <t>2,61; 8,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,1</t>
+          <t>0,61; 3,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,67</t>
+          <t>0,55; 2,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,37</t>
+          <t>2,82; 6,48</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,16</t>
+          <t>0,35; 3,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,4</t>
+          <t>1,5; 5,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,45</t>
+          <t>0,23; 2,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,63</t>
+          <t>0,38; 3,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,86</t>
+          <t>0,73; 3,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,82</t>
+          <t>0,29; 1,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,61</t>
+          <t>0,17; 1,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,78</t>
+          <t>0,58; 2,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,78</t>
+          <t>1,46; 3,68</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,55</t>
+          <t>0,37; 1,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,68</t>
+          <t>1,73; 3,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,18</t>
+          <t>0,78; 2,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,85</t>
+          <t>2,35; 4,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,55</t>
+          <t>0,45; 1,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,23</t>
+          <t>0,79; 2,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,79</t>
+          <t>0,97; 2,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,53</t>
+          <t>2,29; 4,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,29</t>
+          <t>0,5; 1,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,61</t>
+          <t>1,4; 2,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,12</t>
+          <t>1,06; 2,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,21</t>
+          <t>2,54; 4,19</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen transtornos crónicos de la piel (tasa de respuesta: 99,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5716</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1794</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1787</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2604</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7004</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1787</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2679; 10660</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>536; 5026</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>459; 5086</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>682; 6775</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4526</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>651; 6431</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>681; 6178</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3426; 12431</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1868; 8995</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>461; 4987</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2573</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9403</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3305</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5783</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1890</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5516</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4208</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>8816</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4463</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14919</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7512</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>14599</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>635; 6399</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5304; 16060</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1089; 6828</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2781; 11932</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>597; 5071</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2550; 10181</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1653; 9047</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>5078; 15118</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1897; 8879</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>9467; 22561</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3804; 12723</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>9314; 21658</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6613</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2903</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>10168</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4788</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>16782</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6081</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>461; 5178</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>689; 6241</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2894; 12229</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>646; 7446</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>692; 7792</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5555; 17189</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4417</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1927; 9532</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2094; 10516</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>10871; 24975</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1273</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8147</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1842</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2745</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5787</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3217</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4796</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>13935</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4859</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4450</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>611; 6075</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4125; 14896</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>482; 5298</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5230</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>668; 6828</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2232; 11139</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1159; 7629</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>594; 5924</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2014; 9350</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>8470; 21373</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5387</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>18278</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>9273</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>24771</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>11840</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>28751</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>47102</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2517; 10293</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>12212; 26476</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5460; 15438</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15613; 32889</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3276; 12282</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5933; 17055</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7258; 19103</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>17429; 34768</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>6964; 18898</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>20404; 38533</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>15338; 30510</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>36197; 59866</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1020-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Edad-trans_dic.xlsx
@@ -722,32 +722,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,29</t>
+          <t>1,85; 7,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,82</t>
+          <t>0,41; 3,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 8,84</t>
+          <t>0,81; 8,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,58</t>
+          <t>0,57; 5,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,18</t>
+          <t>0,53; 5,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,71</t>
+          <t>0,3; 3,01</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,27</t>
+          <t>1,14; 4,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,52</t>
+          <t>0,72; 3,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,19</t>
+          <t>0,05; 4,03</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,53</t>
+          <t>0,25; 2,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,85</t>
+          <t>2,08; 6,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,24</t>
+          <t>0,72; 3,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,49</t>
+          <t>1,71; 6,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,81</t>
+          <t>0,88; 3,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,51</t>
+          <t>0,61; 3,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 8,28</t>
+          <t>2,65; 8,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,75</t>
+          <t>0,39; 1,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,5</t>
+          <t>1,92; 4,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,72</t>
+          <t>0,92; 2,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,34</t>
+          <t>2,71; 6,59</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,34</t>
+          <t>0,29; 3,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,3</t>
+          <t>0,34; 3,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,07</t>
+          <t>1,89; 7,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,7</t>
+          <t>0,43; 4,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,13</t>
+          <t>0,37; 3,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,09</t>
+          <t>2,5; 8,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,04</t>
+          <t>0,66; 3,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,79</t>
+          <t>0,57; 2,86</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,48</t>
+          <t>2,68; 6,36</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,51</t>
+          <t>0,36; 3,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,41</t>
+          <t>1,46; 5,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,57</t>
+          <t>0,23; 2,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,92</t>
+          <t>0,38; 3,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,65</t>
+          <t>0,86; 3,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,91</t>
+          <t>0,29; 1,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,7</t>
+          <t>0,17; 1,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,69</t>
+          <t>0,59; 2,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,68</t>
+          <t>1,51; 3,89</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,51</t>
+          <t>0,38; 1,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,75</t>
+          <t>1,66; 3,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,19</t>
+          <t>0,76; 2,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,94</t>
+          <t>2,22; 4,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,7</t>
+          <t>0,46; 1,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,28</t>
+          <t>0,79; 2,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,56</t>
+          <t>1,03; 2,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,56</t>
+          <t>2,25; 4,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,35</t>
+          <t>0,52; 1,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,65</t>
+          <t>1,47; 2,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,11</t>
+          <t>1,09; 2,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,19</t>
+          <t>2,56; 4,18</t>
         </is>
       </c>
     </row>
@@ -1650,32 +1650,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2679; 10660</t>
+          <t>2703; 11649</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>536; 5026</t>
+          <t>536; 4754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>459; 5086</t>
+          <t>466; 5071</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>682; 6775</t>
+          <t>686; 6220</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4526</t>
+          <t>0; 3942</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>651; 6431</t>
+          <t>663; 6459</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>681; 6178</t>
+          <t>687; 6844</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3426; 12431</t>
+          <t>3320; 12479</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1868; 8995</t>
+          <t>1843; 8586</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>461; 4987</t>
+          <t>55; 4790</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>635; 6399</t>
+          <t>632; 6489</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5304; 16060</t>
+          <t>4887; 15325</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1089; 6828</t>
+          <t>1517; 7186</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2781; 11932</t>
+          <t>2725; 10700</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>597; 5071</t>
+          <t>597; 5077</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2550; 10181</t>
+          <t>2345; 9964</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1653; 9047</t>
+          <t>1571; 8185</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5078; 15118</t>
+          <t>4830; 15084</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1897; 8879</t>
+          <t>1952; 9457</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9467; 22561</t>
+          <t>9620; 23154</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3804; 12723</t>
+          <t>4313; 13292</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9314; 21658</t>
+          <t>9265; 22542</t>
         </is>
       </c>
     </row>
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6081</t>
+          <t>0; 4961</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>461; 5178</t>
+          <t>456; 4982</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>689; 6241</t>
+          <t>634; 5904</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2894; 12229</t>
+          <t>3274; 12344</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,37 +2086,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>646; 7446</t>
+          <t>678; 7368</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>692; 7792</t>
+          <t>700; 7324</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5555; 17189</t>
+          <t>5315; 17294</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4417</t>
+          <t>0; 4423</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1927; 9532</t>
+          <t>2057; 9505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2094; 10516</t>
+          <t>2145; 10791</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10871; 24975</t>
+          <t>10333; 24535</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4859</t>
+          <t>0; 4591</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4450</t>
+          <t>0; 4256</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>611; 6075</t>
+          <t>618; 5699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4125; 14896</t>
+          <t>4026; 15302</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>482; 5298</t>
+          <t>481; 5076</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5230</t>
+          <t>0; 3645</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>668; 6828</t>
+          <t>669; 6212</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2232; 11139</t>
+          <t>2614; 11841</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1159; 7629</t>
+          <t>1161; 7256</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>594; 5924</t>
+          <t>596; 5914</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2014; 9350</t>
+          <t>2056; 9509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8470; 21373</t>
+          <t>8749; 22609</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2517; 10293</t>
+          <t>2582; 10688</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12212; 26476</t>
+          <t>11700; 25770</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5460; 15438</t>
+          <t>5346; 15234</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15613; 32889</t>
+          <t>14743; 31410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3276; 12282</t>
+          <t>3307; 11581</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5933; 17055</t>
+          <t>5931; 16942</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7258; 19103</t>
+          <t>7657; 19954</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17429; 34768</t>
+          <t>17113; 34309</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6964; 18898</t>
+          <t>7264; 18556</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20404; 38533</t>
+          <t>21325; 40005</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15338; 30510</t>
+          <t>15728; 31162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36197; 59866</t>
+          <t>36581; 59673</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1020-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,91%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,56; 5,57</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,78</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,52; 4,81</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,85; 7,96</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,41; 3,61</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,81; 8,82</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>1,78; 7,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,2</t>
+          <t>0,4; 3,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,94; 9,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,01</t>
+          <t>0,3; 2,97</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,29</t>
+          <t>1,09; 4,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,36</t>
+          <t>0,72; 3,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,03</t>
+          <t>0,46; 4,63</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,01%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,57%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,56</t>
+          <t>0,24; 2,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,54</t>
+          <t>1,04; 4,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,41</t>
+          <t>0,53; 3,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,72</t>
+          <t>2,76; 8,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,0</t>
+          <t>0,28; 2,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,73</t>
+          <t>2,28; 6,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,17</t>
+          <t>0,53; 3,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,26</t>
+          <t>1,88; 7,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,87</t>
+          <t>0,38; 1,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,62</t>
+          <t>1,95; 4,48</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,84</t>
+          <t>0,83; 2,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,59</t>
+          <t>2,78; 6,85</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,22</t>
+          <t>0,6; 4,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,13</t>
+          <t>0,38; 4,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,13</t>
+          <t>2,54; 8,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,65</t>
+          <t>0,3; 3,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,88</t>
+          <t>0,33; 3,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 8,14</t>
+          <t>2,04; 7,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,03</t>
+          <t>0,58; 3,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,86</t>
+          <t>0,55; 2,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,36</t>
+          <t>2,76; 6,59</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,23; 2,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,29</t>
+          <t>0,4; 3,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,56</t>
+          <t>0,92; 4,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,46</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,57</t>
+          <t>0,35; 3,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,88</t>
+          <t>1,65; 6,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,81</t>
+          <t>0,29; 1,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,69</t>
+          <t>0,17; 1,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,74</t>
+          <t>0,58; 2,78</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,89</t>
+          <t>1,6; 4,15</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,57</t>
+          <t>0,45; 1,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,65</t>
+          <t>0,78; 2,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,16</t>
+          <t>1,03; 2,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,72</t>
+          <t>2,35; 4,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,6</t>
+          <t>0,31; 1,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,26</t>
+          <t>1,72; 3,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,68</t>
+          <t>0,75; 2,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,5</t>
+          <t>2,51; 5,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,32</t>
+          <t>0,52; 1,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,75</t>
+          <t>1,46; 2,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,15</t>
+          <t>1,09; 2,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,18</t>
+          <t>2,66; 4,49</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,49 +1577,49 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2604</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>5716</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>1794</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2721</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2604</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2721</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>7004</t>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1800</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>686; 6760</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4018</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>649; 5969</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2703; 11649</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>536; 4754</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>466; 5071</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>686; 6220</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3942</t>
+          <t>2603; 11139</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>663; 6459</t>
+          <t>532; 5247</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>489; 4903</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>687; 6844</t>
+          <t>675; 6768</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3320; 12479</t>
+          <t>3160; 12182</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1843; 8586</t>
+          <t>1839; 8770</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55; 4790</t>
+          <t>474; 4756</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1890</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5516</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4208</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7958</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2573</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9403</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3305</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5783</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1890</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5516</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4208</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>13593</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>632; 6489</t>
+          <t>598; 5572</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4887; 15325</t>
+          <t>2787; 11001</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1517; 7186</t>
+          <t>1375; 9015</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2725; 10700</t>
+          <t>4346; 13507</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>597; 5077</t>
+          <t>713; 6414</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2345; 9964</t>
+          <t>5349; 16002</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1571; 8185</t>
+          <t>1107; 6982</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4830; 15084</t>
+          <t>2730; 11513</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1952; 9457</t>
+          <t>1905; 9035</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9620; 23154</t>
+          <t>9790; 22493</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4313; 13292</t>
+          <t>3903; 12351</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9265; 22542</t>
+          <t>8426; 20743</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2903</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9814</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1439</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1885</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2123</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6613</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2903</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3148</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>16746</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4961</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>456; 4982</t>
+          <t>958; 7144</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>634; 5904</t>
+          <t>708; 8002</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3274; 12344</t>
+          <t>5087; 16937</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5139</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>678; 7368</t>
+          <t>461; 5330</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>700; 7324</t>
+          <t>631; 5932</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5315; 17294</t>
+          <t>3566; 13067</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4423</t>
+          <t>0; 5001</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2057; 9505</t>
+          <t>1831; 9715</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2145; 10791</t>
+          <t>2087; 10093</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10333; 24535</t>
+          <t>10343; 24696</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1842</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2745</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1375</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1273</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2051</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1842</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2745</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13935</t>
+          <t>14829</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4591</t>
+          <t>482; 5039</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4256</t>
+          <t>0; 4631</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>618; 5699</t>
+          <t>701; 6315</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4026; 15302</t>
+          <t>2691; 12576</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>481; 5076</t>
+          <t>0; 4279</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3645</t>
+          <t>0; 4005</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>669; 6212</t>
+          <t>612; 5477</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2614; 11841</t>
+          <t>4241; 16204</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1161; 7256</t>
+          <t>1170; 7264</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>596; 5914</t>
+          <t>595; 5626</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2056; 9509</t>
+          <t>2029; 9667</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8749; 22609</t>
+          <t>8811; 22819</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23886</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>5387</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>18278</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>9273</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>22331</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6453</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10473</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>12706</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>46968</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2582; 10688</t>
+          <t>3225; 11189</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>11700; 25770</t>
+          <t>5802; 16679</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5346; 15234</t>
+          <t>7671; 20758</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14743; 31410</t>
+          <t>16439; 33216</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3307; 11581</t>
+          <t>2129; 10536</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5931; 16942</t>
+          <t>12126; 26014</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7657; 19954</t>
+          <t>5285; 15348</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17113; 34309</t>
+          <t>15793; 33047</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7264; 18556</t>
+          <t>7253; 18105</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21325; 40005</t>
+          <t>21301; 38030</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15728; 31162</t>
+          <t>15747; 30705</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36581; 59673</t>
+          <t>35412; 59721</t>
         </is>
       </c>
     </row>
